--- a/tables/xls/it/95_Movimentazioni consumabili.xlsx
+++ b/tables/xls/it/95_Movimentazioni consumabili.xlsx
@@ -132,7 +132,7 @@
     <t>Testo - Elenco di valori</t>
   </si>
   <si>
-    <t>Carico,Scarico,Movimentazione</t>
+    <t>CARICO,SCARICO,TRASFERIMENTO</t>
   </si>
   <si>
     <t>ART.</t>
@@ -141,10 +141,10 @@
     <t>Q.TA'</t>
   </si>
   <si>
+    <t>Numero Decimale</t>
+  </si>
+  <si>
     <t>UdM</t>
-  </si>
-  <si>
-    <t>Numero Decimale</t>
   </si>
   <si>
     <t>MAG. ORIG.</t>
@@ -654,7 +654,7 @@
         <v>40</v>
       </c>
       <c r="F3" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="G3" t="s">
         <v>43</v>
@@ -686,10 +686,10 @@
         <v>34</v>
       </c>
       <c r="E4" t="s">
+        <v>41</v>
+      </c>
+      <c r="F4" t="s">
         <v>34</v>
-      </c>
-      <c r="F4" t="s">
-        <v>42</v>
       </c>
       <c r="G4" t="s">
         <v>34</v>
